--- a/Workpulse_Build_Size_Optimization_Report.xlsx
+++ b/Workpulse_Build_Size_Optimization_Report.xlsx
@@ -634,7 +634,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Audit Completed: 2026-09-29 06:39:02 UTC  |  Application Version: 1.0  |  Regression Tests Passed: 346/346 (100%)</t>
+          <t>Audit Completed: 2026-09-29 09:19:48 UTC  |  Application Version: 1.0  |  Regression Tests Passed: 346/346 (100%)</t>
         </is>
       </c>
     </row>
